--- a/12627430.xlsx
+++ b/12627430.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\divyani patidar\gitdemo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{694AC67D-D9B0-4193-9EA6-3CF786BC70EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C176D104-0DAF-4C48-BF63-DEB0FAA5D495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,13 +228,16 @@
   <si>
     <t>Had  a Good Study Session</t>
   </si>
+  <si>
+    <t>Had n Normal Day</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -397,7 +399,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -417,9 +419,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -433,7 +432,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -449,12 +448,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -939,72 +941,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="28">
         <v>12627430</v>
       </c>
-      <c r="G2" s="14"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="14"/>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
@@ -1050,146 +1052,146 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="20" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="27">
+    <row r="6" spans="1:14" s="17" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="24">
         <v>46251</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>380</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="13">
         <v>15</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="13">
         <v>300</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="13">
         <v>60</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="13">
         <v>360</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="13">
         <v>6</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="13">
         <v>90</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="14">
         <f>IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1205</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="14">
         <f t="shared" ref="J6:J69" si="0">IF(I6="","",1440-I6)</f>
         <v>235</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="18" t="s">
+      <c r="M6" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="26" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="21">
+    <row r="7" spans="1:14" s="23" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="18">
         <v>46252</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="19">
         <v>360</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>10</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="19">
         <v>300</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="19">
         <v>90</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="19">
         <v>420</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="19">
         <v>7</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="19">
         <v>75</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="20">
         <f t="shared" ref="I7:I69" si="1">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>1255</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="20">
         <f t="shared" si="0"/>
         <v>185</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="24" t="s">
+      <c r="L7" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="26" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="21">
+    <row r="8" spans="1:14" s="23" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="18">
         <v>46253</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="19">
         <v>380</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="19">
         <v>15</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="19">
         <v>400</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="19">
         <v>80</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="19">
         <v>360</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="19">
         <v>6</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="19">
         <v>70</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="20">
         <f t="shared" si="1"/>
         <v>1305</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="20">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="25" t="s">
+      <c r="N8" s="22" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="21">
+      <c r="A9" s="18">
         <v>46254</v>
       </c>
       <c r="B9" s="4">
@@ -1230,12 +1232,12 @@
       <c r="M9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="28" t="s">
+      <c r="N9" s="25" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="21">
+      <c r="A10" s="18">
         <v>46255</v>
       </c>
       <c r="B10" s="4">
@@ -1276,7 +1278,7 @@
       <c r="M10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="28" t="s">
+      <c r="N10" s="25" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1322,7 +1324,7 @@
       <c r="M11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="28" t="s">
+      <c r="N11" s="25" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1368,7 +1370,7 @@
       <c r="M12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N12" s="28" t="s">
+      <c r="N12" s="25" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1414,7 +1416,7 @@
       <c r="M13" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N13" s="28" t="s">
+      <c r="N13" s="25" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1460,7 +1462,7 @@
       <c r="M14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N14" s="28" t="s">
+      <c r="N14" s="25" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1506,7 +1508,7 @@
       <c r="M15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N15" s="28" t="s">
+      <c r="N15" s="25" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1552,7 +1554,7 @@
       <c r="M16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="N16" s="28" t="s">
+      <c r="N16" s="25" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1598,7 +1600,7 @@
       <c r="M17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="N17" s="28" t="s">
+      <c r="N17" s="25" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1644,7 +1646,7 @@
       <c r="M18" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="N18" s="28" t="s">
+      <c r="N18" s="25" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1690,163 +1692,331 @@
       <c r="M19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="28" t="s">
+      <c r="N19" s="25" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="5" t="str">
+      <c r="A20" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="4">
+        <v>420</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>350</v>
+      </c>
+      <c r="E20" s="4">
+        <v>150</v>
+      </c>
+      <c r="F20" s="4">
+        <v>200</v>
+      </c>
+      <c r="G20" s="4">
+        <v>4</v>
+      </c>
+      <c r="H20" s="4">
+        <v>300</v>
+      </c>
+      <c r="I20" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J20" s="5" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J20" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="5" t="str">
+      <c r="A21" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="4">
+        <v>450</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>250</v>
+      </c>
+      <c r="E21" s="4">
+        <v>200</v>
+      </c>
+      <c r="F21" s="4">
+        <v>350</v>
+      </c>
+      <c r="G21" s="4">
+        <v>7</v>
+      </c>
+      <c r="H21" s="4">
+        <v>150</v>
+      </c>
+      <c r="I21" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J21" s="5" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J21" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5" t="str">
+      <c r="A22" s="3">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="4">
+        <v>300</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>340</v>
+      </c>
+      <c r="E22" s="4">
+        <v>180</v>
+      </c>
+      <c r="F22" s="4">
+        <v>350</v>
+      </c>
+      <c r="G22" s="4">
+        <v>7</v>
+      </c>
+      <c r="H22" s="4">
+        <v>200</v>
+      </c>
+      <c r="I22" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J22" s="5" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J22" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="7"/>
+        <v>70</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="5" t="str">
+      <c r="A23" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="4">
+        <v>350</v>
+      </c>
+      <c r="C23" s="4">
+        <v>20</v>
+      </c>
+      <c r="D23" s="4">
+        <v>400</v>
+      </c>
+      <c r="E23" s="4">
+        <v>200</v>
+      </c>
+      <c r="F23" s="4">
+        <v>200</v>
+      </c>
+      <c r="G23" s="4">
+        <v>4</v>
+      </c>
+      <c r="H23" s="4">
+        <v>150</v>
+      </c>
+      <c r="I23" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J23" s="5" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J23" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="7"/>
+        <v>120</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5" t="str">
+      <c r="A24" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="4">
+        <v>380</v>
+      </c>
+      <c r="C24" s="4">
+        <v>30</v>
+      </c>
+      <c r="D24" s="4">
+        <v>350</v>
+      </c>
+      <c r="E24" s="4">
+        <v>210</v>
+      </c>
+      <c r="F24" s="4">
+        <v>250</v>
+      </c>
+      <c r="G24" s="4">
+        <v>5</v>
+      </c>
+      <c r="H24" s="4">
+        <v>220</v>
+      </c>
+      <c r="I24" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J24" s="5" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J24" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="3"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="5" t="str">
+      <c r="A25" s="3">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="4">
+        <v>390</v>
+      </c>
+      <c r="C25" s="4">
+        <v>15</v>
+      </c>
+      <c r="D25" s="4">
+        <v>450</v>
+      </c>
+      <c r="E25" s="4">
+        <v>250</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <v>250</v>
+      </c>
+      <c r="I25" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J25" s="5" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J25" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="7"/>
+        <v>85</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="3"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5" t="str">
+      <c r="A26" s="3">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="4">
+        <v>390</v>
+      </c>
+      <c r="C26" s="4">
+        <v>20</v>
+      </c>
+      <c r="D26" s="4">
+        <v>400</v>
+      </c>
+      <c r="E26" s="4">
+        <v>300</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <v>300</v>
+      </c>
+      <c r="I26" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J26" s="5" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J26" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="7"/>
+        <v>30</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>

--- a/12627430.xlsx
+++ b/12627430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\divyani patidar\gitdemo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C176D104-0DAF-4C48-BF63-DEB0FAA5D495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AF2C10-7634-472D-8B90-8283964F5C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,33 @@
   </si>
   <si>
     <t>Had n Normal Day</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Had a usual Day</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Day was  Fine And manageable</t>
+  </si>
+  <si>
+    <t>Made Good Progress In Studies</t>
+  </si>
+  <si>
+    <t>Revicsed and Practiced Today's Work</t>
+  </si>
+  <si>
+    <t>Studied Well Today</t>
+  </si>
+  <si>
+    <t>Attented  Classes And Studied</t>
+  </si>
+  <si>
+    <t>Had a Normal Study Day</t>
   </si>
 </sst>
 </file>
@@ -2019,268 +2046,556 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="3"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5" t="str">
+      <c r="A27" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="4">
+        <v>300</v>
+      </c>
+      <c r="C27" s="4">
+        <v>20</v>
+      </c>
+      <c r="D27" s="4">
+        <v>400</v>
+      </c>
+      <c r="E27" s="4">
+        <v>80</v>
+      </c>
+      <c r="F27" s="4">
+        <v>200</v>
+      </c>
+      <c r="G27" s="4">
+        <v>4</v>
+      </c>
+      <c r="H27" s="4">
+        <v>420</v>
+      </c>
+      <c r="I27" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J27" s="5" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J27" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="3"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="5" t="str">
+      <c r="A28" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="4">
+        <v>350</v>
+      </c>
+      <c r="C28" s="4">
+        <v>30</v>
+      </c>
+      <c r="D28" s="4">
+        <v>310</v>
+      </c>
+      <c r="E28" s="4">
+        <v>60</v>
+      </c>
+      <c r="F28" s="4">
+        <v>350</v>
+      </c>
+      <c r="G28" s="4">
+        <v>7</v>
+      </c>
+      <c r="H28" s="4">
+        <v>300</v>
+      </c>
+      <c r="I28" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J28" s="5" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J28" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="3"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="5" t="str">
+      <c r="A29" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="4">
+        <v>350</v>
+      </c>
+      <c r="C29" s="4">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4">
+        <v>350</v>
+      </c>
+      <c r="E29" s="4">
+        <v>60</v>
+      </c>
+      <c r="F29" s="4">
+        <v>350</v>
+      </c>
+      <c r="G29" s="4">
+        <v>7</v>
+      </c>
+      <c r="H29" s="4">
+        <v>250</v>
+      </c>
+      <c r="I29" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J29" s="5" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J29" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="5" t="str">
+      <c r="A30" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="4">
+        <v>250</v>
+      </c>
+      <c r="C30" s="4">
+        <v>30</v>
+      </c>
+      <c r="D30" s="4">
+        <v>350</v>
+      </c>
+      <c r="E30" s="4">
+        <v>50</v>
+      </c>
+      <c r="F30" s="4">
+        <v>200</v>
+      </c>
+      <c r="G30" s="4">
+        <v>4</v>
+      </c>
+      <c r="H30" s="4">
+        <v>400</v>
+      </c>
+      <c r="I30" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J30" s="5" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J30" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="7"/>
+        <v>160</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5" t="str">
+      <c r="A31" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="4">
+        <v>320</v>
+      </c>
+      <c r="C31" s="4">
+        <v>30</v>
+      </c>
+      <c r="D31" s="4">
+        <v>250</v>
+      </c>
+      <c r="E31" s="4">
+        <v>100</v>
+      </c>
+      <c r="F31" s="4">
+        <v>250</v>
+      </c>
+      <c r="G31" s="4">
+        <v>5</v>
+      </c>
+      <c r="H31" s="4">
+        <v>380</v>
+      </c>
+      <c r="I31" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J31" s="5" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J31" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="7"/>
+        <v>110</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="5" t="str">
+      <c r="A32" s="3">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="4">
+        <v>350</v>
+      </c>
+      <c r="C32" s="4">
+        <v>30</v>
+      </c>
+      <c r="D32" s="4">
+        <v>540</v>
+      </c>
+      <c r="E32" s="4">
+        <v>200</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4">
+        <v>300</v>
+      </c>
+      <c r="I32" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J32" s="5" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J32" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="7"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="3"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5" t="str">
+        <v>20</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="3">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="4">
+        <v>450</v>
+      </c>
+      <c r="C33" s="4">
+        <v>30</v>
+      </c>
+      <c r="D33" s="4">
+        <v>600</v>
+      </c>
+      <c r="E33" s="4">
+        <v>180</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4">
+        <v>180</v>
+      </c>
+      <c r="I33" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="5" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J33" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="3"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="5" t="str">
+      <c r="A34" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="4">
+        <v>360</v>
+      </c>
+      <c r="C34" s="4">
+        <v>40</v>
+      </c>
+      <c r="D34" s="4">
+        <v>500</v>
+      </c>
+      <c r="E34" s="4">
+        <v>120</v>
+      </c>
+      <c r="F34" s="4">
+        <v>200</v>
+      </c>
+      <c r="G34" s="4">
+        <v>4</v>
+      </c>
+      <c r="H34" s="4">
+        <v>180</v>
+      </c>
+      <c r="I34" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J34" s="5" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J34" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="5" t="str">
+      <c r="A35" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="4">
+        <v>400</v>
+      </c>
+      <c r="C35" s="4">
+        <v>15</v>
+      </c>
+      <c r="D35" s="4">
+        <v>340</v>
+      </c>
+      <c r="E35" s="4">
+        <v>60</v>
+      </c>
+      <c r="F35" s="4">
+        <v>350</v>
+      </c>
+      <c r="G35" s="4">
+        <v>7</v>
+      </c>
+      <c r="H35" s="4">
+        <v>220</v>
+      </c>
+      <c r="I35" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="5" t="str">
+        <v>1385</v>
+      </c>
+      <c r="J35" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5" t="str">
+      <c r="A36" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="4">
+        <v>350</v>
+      </c>
+      <c r="C36" s="4">
+        <v>15</v>
+      </c>
+      <c r="D36" s="4">
+        <v>340</v>
+      </c>
+      <c r="E36" s="4">
+        <v>60</v>
+      </c>
+      <c r="F36" s="4">
+        <v>350</v>
+      </c>
+      <c r="G36" s="4">
+        <v>7</v>
+      </c>
+      <c r="H36" s="4">
+        <v>250</v>
+      </c>
+      <c r="I36" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J36" s="5" t="str">
+        <v>1365</v>
+      </c>
+      <c r="J36" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="7"/>
+        <v>75</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="3"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="5" t="str">
+      <c r="A37" s="3">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="4">
+        <v>420</v>
+      </c>
+      <c r="C37" s="4">
+        <v>30</v>
+      </c>
+      <c r="D37" s="4">
+        <v>350</v>
+      </c>
+      <c r="E37" s="4">
+        <v>50</v>
+      </c>
+      <c r="F37" s="4">
+        <v>200</v>
+      </c>
+      <c r="G37" s="4">
+        <v>4</v>
+      </c>
+      <c r="H37" s="4">
+        <v>300</v>
+      </c>
+      <c r="I37" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J37" s="5" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J37" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="7"/>
+        <v>90</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="3"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5" t="str">
+      <c r="A38" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="4">
+        <v>250</v>
+      </c>
+      <c r="C38" s="4">
+        <v>30</v>
+      </c>
+      <c r="D38" s="4">
+        <v>420</v>
+      </c>
+      <c r="E38" s="4">
+        <v>80</v>
+      </c>
+      <c r="F38" s="4">
+        <v>250</v>
+      </c>
+      <c r="G38" s="4">
+        <v>5</v>
+      </c>
+      <c r="H38" s="4">
+        <v>380</v>
+      </c>
+      <c r="I38" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J38" s="5" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J38" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="7"/>
+        <v>30</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>

--- a/12627430.xlsx
+++ b/12627430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\divyani patidar\gitdemo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AF2C10-7634-472D-8B90-8283964F5C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FABFA2-F194-4F2F-8EF1-A9670C3105D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Had a Normal Study Day</t>
+  </si>
+  <si>
+    <t>CA System Issue-unable to attempt</t>
   </si>
 </sst>
 </file>
@@ -2597,27 +2600,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="3"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="5" t="str">
+    <row r="39" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="4">
+        <v>300</v>
+      </c>
+      <c r="C39" s="4">
+        <v>50</v>
+      </c>
+      <c r="D39" s="4">
+        <v>600</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4">
+        <v>120</v>
+      </c>
+      <c r="I39" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J39" s="5" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J39" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="7"/>
+        <v>370</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>

--- a/12627430.xlsx
+++ b/12627430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\divyani patidar\gitdemo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FABFA2-F194-4F2F-8EF1-A9670C3105D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A05440E-4FB4-4EEE-8294-2ECC771DB7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2647,26 +2647,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="3"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5" t="str">
+      <c r="A40" s="3">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="4">
+        <v>540</v>
+      </c>
+      <c r="C40" s="4">
+        <v>30</v>
+      </c>
+      <c r="D40" s="4">
+        <v>600</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4">
+        <v>120</v>
+      </c>
+      <c r="I40" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J40" s="5" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J40" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
-      <c r="N40" s="7"/>
+        <v>150</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>

--- a/12627430.xlsx
+++ b/12627430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\divyani patidar\gitdemo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A05440E-4FB4-4EEE-8294-2ECC771DB7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA807C45-78BC-4366-B851-47A7AE98EFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2693,26 +2693,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="3"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="5" t="str">
+      <c r="A41" s="3">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="4">
+        <v>480</v>
+      </c>
+      <c r="C41" s="4">
+        <v>30</v>
+      </c>
+      <c r="D41" s="4">
+        <v>400</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4">
+        <v>200</v>
+      </c>
+      <c r="G41" s="4">
+        <v>4</v>
+      </c>
+      <c r="H41" s="4">
+        <v>60</v>
+      </c>
+      <c r="I41" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J41" s="5" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J41" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="7"/>
+        <v>270</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>

--- a/12627430.xlsx
+++ b/12627430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\divyani patidar\gitdemo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA807C45-78BC-4366-B851-47A7AE98EFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F8659F-7778-4D6F-BCCF-0B1814375DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2739,26 +2739,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="3"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="5" t="str">
+      <c r="A42" s="3">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="4">
+        <v>360</v>
+      </c>
+      <c r="C42" s="4">
+        <v>25</v>
+      </c>
+      <c r="D42" s="4">
+        <v>400</v>
+      </c>
+      <c r="E42" s="4">
+        <v>150</v>
+      </c>
+      <c r="F42" s="4">
+        <v>350</v>
+      </c>
+      <c r="G42" s="4">
+        <v>7</v>
+      </c>
+      <c r="H42" s="4">
+        <v>80</v>
+      </c>
+      <c r="I42" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J42" s="5" t="str">
+        <v>1365</v>
+      </c>
+      <c r="J42" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="7"/>
+        <v>75</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>

--- a/12627430.xlsx
+++ b/12627430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\divyani patidar\gitdemo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F8659F-7778-4D6F-BCCF-0B1814375DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCEB1A1-BD29-43D4-97F9-B77A8A8C601E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2749,7 +2749,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="4">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E42" s="4">
         <v>150</v>
@@ -2765,11 +2765,11 @@
       </c>
       <c r="I42" s="5">
         <f t="shared" si="1"/>
-        <v>1365</v>
+        <v>1315</v>
       </c>
       <c r="J42" s="5">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>50</v>
@@ -2785,70 +2785,142 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="3"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="5" t="str">
+      <c r="A43" s="3">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="4">
+        <v>450</v>
+      </c>
+      <c r="C43" s="4">
+        <v>30</v>
+      </c>
+      <c r="D43" s="4">
+        <v>420</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4">
+        <v>350</v>
+      </c>
+      <c r="G43" s="4">
+        <v>7</v>
+      </c>
+      <c r="H43" s="4">
+        <v>100</v>
+      </c>
+      <c r="I43" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J43" s="5" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J43" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="7"/>
+        <v>90</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="3"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="5" t="str">
+      <c r="A44" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="4">
+        <v>480</v>
+      </c>
+      <c r="C44" s="4">
+        <v>30</v>
+      </c>
+      <c r="D44" s="4">
+        <v>400</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4">
+        <v>200</v>
+      </c>
+      <c r="G44" s="4">
+        <v>4</v>
+      </c>
+      <c r="H44" s="4">
+        <v>200</v>
+      </c>
+      <c r="I44" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J44" s="5" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J44" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="7"/>
+        <v>130</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="3"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="5" t="str">
+      <c r="A45" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="4">
+        <v>450</v>
+      </c>
+      <c r="C45" s="4">
+        <v>30</v>
+      </c>
+      <c r="D45" s="4">
+        <v>440</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4">
+        <v>250</v>
+      </c>
+      <c r="G45" s="4">
+        <v>5</v>
+      </c>
+      <c r="H45" s="4">
+        <v>200</v>
+      </c>
+      <c r="I45" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J45" s="5" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J45" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="7"/>
+        <v>70</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
